--- a/testData/dataTransferFondos.xlsx
+++ b/testData/dataTransferFondos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="23">
   <si>
     <t>Estatus de la prueba</t>
   </si>

--- a/testData/dataTransferFondos.xlsx
+++ b/testData/dataTransferFondos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="23">
   <si>
     <t>Estatus de la prueba</t>
   </si>

--- a/testData/dataTransferFondos.xlsx
+++ b/testData/dataTransferFondos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="23">
   <si>
     <t>Estatus de la prueba</t>
   </si>
